--- a/posts/assurance_maladie/data_final_am.xlsx
+++ b/posts/assurance_maladie/data_final_am.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\posts\assurance_maladie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EAD2CB-864E-4215-BDFF-233BD7C973CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85156B68-7DC9-4D10-A844-3CCB429B8C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{6F1D0405-E567-46E6-8D14-14BA1834753A}"/>
+    <workbookView xWindow="-2993" yWindow="968" windowWidth="28486" windowHeight="14969" activeTab="1" xr2:uid="{6F1D0405-E567-46E6-8D14-14BA1834753A}"/>
   </bookViews>
   <sheets>
     <sheet name="sources" sheetId="1" r:id="rId1"/>
     <sheet name="graphique 1" sheetId="2" r:id="rId2"/>
     <sheet name="graphique2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Year</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>Q5</t>
+  </si>
+  <si>
+    <t>tx_prime</t>
+  </si>
+  <si>
+    <t>tx_couts</t>
   </si>
 </sst>
 </file>
@@ -493,7 +499,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC51F8C4-6D55-40E2-9AE7-552D21CEB599}">
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="4" max="4" width="22.86328125" customWidth="1"/>
@@ -501,7 +507,7 @@
     <col min="6" max="6" width="21.1328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -547,8 +553,14 @@
       <c r="O1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P1" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1999</v>
       </c>
@@ -593,7 +605,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -640,8 +652,16 @@
         <f t="shared" ref="O3:O27" si="0">D3/$D$2*100</f>
         <v>103.63146777844845</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P3">
+        <f>LOG(I3)-LOG(I2)</f>
+        <v>2.6941627959029546E-2</v>
+      </c>
+      <c r="Q3">
+        <f>LOG(F3)-LOG(F2)</f>
+        <v>-4.8265521725734395E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -688,8 +708,16 @@
         <f t="shared" si="0"/>
         <v>109.43734345489334</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P4">
+        <f t="shared" ref="P4:P27" si="1">LOG(I4)-LOG(I3)</f>
+        <v>1.8772430981838006E-2</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q27" si="2">LOG(F4)-LOG(F3)</f>
+        <v>1.5228366887252154E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -736,8 +764,16 @@
         <f t="shared" si="0"/>
         <v>113.01395537656742</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P5">
+        <f t="shared" si="1"/>
+        <v>1.6491749878845052E-2</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>1.8847468728113048E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2003</v>
       </c>
@@ -784,8 +820,16 @@
         <f t="shared" si="0"/>
         <v>116.4163456178017</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>3.7471714941572642E-3</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>1.1151059684289866E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2004</v>
       </c>
@@ -832,8 +876,16 @@
         <f t="shared" si="0"/>
         <v>120.13795704307373</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>5.5608247812193312E-3</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>3.7877620958437497E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>2005</v>
       </c>
@@ -880,8 +932,16 @@
         <f t="shared" si="0"/>
         <v>121.75920652302806</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>3.6680495236023347E-3</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>-7.1740961845483397E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>2006</v>
       </c>
@@ -928,8 +988,16 @@
         <f t="shared" si="0"/>
         <v>122.5206745760002</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>1.2599563190851093E-2</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>-2.1147170546480409E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -976,8 +1044,16 @@
         <f t="shared" si="0"/>
         <v>126.98426843524824</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>2.1236936298554276E-3</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>-7.4648588254756509E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>2008</v>
       </c>
@@ -1024,8 +1100,16 @@
         <f t="shared" si="0"/>
         <v>132.36399131139274</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P11">
+        <f t="shared" si="1"/>
+        <v>4.9152689154019491E-3</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>5.2596014831387539E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>2009</v>
       </c>
@@ -1072,8 +1156,16 @@
         <f t="shared" si="0"/>
         <v>136.51027845647599</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P12">
+        <f t="shared" si="1"/>
+        <v>7.6133253265364687E-3</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>2.693315144322761E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>2010</v>
       </c>
@@ -1120,8 +1212,16 @@
         <f t="shared" si="0"/>
         <v>138.20549128346155</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P13">
+        <f t="shared" si="1"/>
+        <v>2.7256186517964576E-2</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>-5.3349895762571098E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>2011</v>
       </c>
@@ -1168,8 +1268,16 @@
         <f t="shared" si="0"/>
         <v>140.70258064044089</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P14">
+        <f t="shared" si="1"/>
+        <v>2.0452269649257726E-2</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>4.8907312779973289E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>2012</v>
       </c>
@@ -1216,8 +1324,16 @@
         <f t="shared" si="0"/>
         <v>144.17285803823299</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>4.2818112660882868E-3</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>9.82475003270733E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>2013</v>
       </c>
@@ -1264,8 +1380,16 @@
         <f t="shared" si="0"/>
         <v>148.59005038340374</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>6.6444123565276847E-3</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>1.076311426889065E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>2014</v>
       </c>
@@ -1312,8 +1436,16 @@
         <f t="shared" si="0"/>
         <v>150.39276789002517</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P17">
+        <f t="shared" si="1"/>
+        <v>-4.7459234398147032E-2</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>3.2945074232559879E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>2015</v>
       </c>
@@ -1360,8 +1492,16 @@
         <f t="shared" si="0"/>
         <v>153.48339393595819</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P18">
+        <f t="shared" si="1"/>
+        <v>-7.0782972506462372E-3</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="2"/>
+        <v>1.2222894414801955E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>2016</v>
       </c>
@@ -1408,8 +1548,16 @@
         <f t="shared" si="0"/>
         <v>157.1771937860276</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P19">
+        <f t="shared" si="1"/>
+        <v>-1.2759072323651477E-2</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>8.7188484265796617E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>2017</v>
       </c>
@@ -1456,8 +1604,16 @@
         <f t="shared" si="0"/>
         <v>159.67649446208637</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P20">
+        <f t="shared" si="1"/>
+        <v>1.7462608244209754E-3</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>6.6260874506309797E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -1504,8 +1660,16 @@
         <f t="shared" si="0"/>
         <v>161.16116257862018</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P21">
+        <f>LOG(I21)-LOG(I20)</f>
+        <v>2.2084649366933107E-2</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>-8.3365106053410187E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -1552,8 +1716,16 @@
         <f t="shared" si="0"/>
         <v>165.09771305308067</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="2"/>
+        <v>9.0985577963027531E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -1600,8 +1772,16 @@
         <f t="shared" si="0"/>
         <v>167.57935042884387</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P23">
+        <f t="shared" si="1"/>
+        <v>3.3114334955719471E-4</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="2"/>
+        <v>2.2102403374825164E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>2021</v>
       </c>
@@ -1648,8 +1828,16 @@
         <f t="shared" si="0"/>
         <v>177.40633573740303</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P24">
+        <f>LOG(I24)-LOG(I23)</f>
+        <v>-1.3260910513928081E-3</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="2"/>
+        <v>-1.1262833223926183E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>2022</v>
       </c>
@@ -1696,8 +1884,16 @@
         <f t="shared" si="0"/>
         <v>181.19243434354425</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P25">
+        <f t="shared" si="1"/>
+        <v>-1.6633282756637335E-3</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="2"/>
+        <v>-1.3253749316398222E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -1744,8 +1940,16 @@
         <f t="shared" si="0"/>
         <v>183.19104478724321</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>-2.3394141780102018E-3</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="2"/>
+        <v>3.4252060846016175E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -1791,6 +1995,14 @@
       <c r="O27">
         <f t="shared" si="0"/>
         <v>186.88690330628964</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="1"/>
+        <v>-5.055871789888311E-3</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="2"/>
+        <v>3.0256232436358665E-3</v>
       </c>
     </row>
   </sheetData>

--- a/posts/assurance_maladie/data_final_am.xlsx
+++ b/posts/assurance_maladie/data_final_am.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\posts\assurance_maladie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85156B68-7DC9-4D10-A844-3CCB429B8C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{314F701F-CED1-46BD-B9D9-2A0E670CEC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2993" yWindow="968" windowWidth="28486" windowHeight="14969" activeTab="1" xr2:uid="{6F1D0405-E567-46E6-8D14-14BA1834753A}"/>
+    <workbookView xWindow="300" yWindow="615" windowWidth="28485" windowHeight="14970" activeTab="1" xr2:uid="{6F1D0405-E567-46E6-8D14-14BA1834753A}"/>
   </bookViews>
   <sheets>
     <sheet name="sources" sheetId="1" r:id="rId1"/>
     <sheet name="graphique 1" sheetId="2" r:id="rId2"/>
     <sheet name="graphique2" sheetId="3" r:id="rId3"/>
+    <sheet name="graphique3" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="41">
   <si>
     <t>Year</t>
   </si>
@@ -129,6 +130,27 @@
   </si>
   <si>
     <t>tx_couts</t>
+  </si>
+  <si>
+    <t>Subventions selon le LAMal per ménage et par année 3 en francs</t>
+  </si>
+  <si>
+    <t>Taux de bénéficiaires en % 2</t>
+  </si>
+  <si>
+    <t>Nombre des Bénéficiaires 1</t>
+  </si>
+  <si>
+    <t>Nombre des ménages</t>
+  </si>
+  <si>
+    <t>primes_moyenne_par_assures</t>
+  </si>
+  <si>
+    <t>base100_prime</t>
+  </si>
+  <si>
+    <t>base100_subsides</t>
   </si>
 </sst>
 </file>
@@ -2228,4 +2250,768 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E2B8738-45AB-4236-AAFB-A846B99E2A26}">
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2">
+        <v>1996</v>
+      </c>
+      <c r="B2">
+        <v>1939.5244786551</v>
+      </c>
+      <c r="C2">
+        <v>0.23</v>
+      </c>
+      <c r="D2">
+        <v>1651697</v>
+      </c>
+      <c r="E2">
+        <v>756457</v>
+      </c>
+      <c r="F2">
+        <v>1538.9</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3">
+        <v>1997</v>
+      </c>
+      <c r="B3">
+        <v>2016.5343367646201</v>
+      </c>
+      <c r="C3">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D3">
+        <v>1955994</v>
+      </c>
+      <c r="E3">
+        <v>988940</v>
+      </c>
+      <c r="F3">
+        <v>1663.9</v>
+      </c>
+      <c r="G3">
+        <v>108.1226850347651</v>
+      </c>
+      <c r="H3">
+        <v>103.97055355356588</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4">
+        <v>1998</v>
+      </c>
+      <c r="B4">
+        <v>2075.82951268125</v>
+      </c>
+      <c r="C4">
+        <v>0.311</v>
+      </c>
+      <c r="D4">
+        <v>2240522</v>
+      </c>
+      <c r="E4">
+        <v>1178551</v>
+      </c>
+      <c r="F4">
+        <v>1753.7</v>
+      </c>
+      <c r="G4">
+        <v>113.95802196374034</v>
+      </c>
+      <c r="H4">
+        <v>107.0277552836387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5">
+        <v>1999</v>
+      </c>
+      <c r="B5">
+        <v>2186.56535456755</v>
+      </c>
+      <c r="C5">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="D5">
+        <v>2334267</v>
+      </c>
+      <c r="E5">
+        <v>1230090</v>
+      </c>
+      <c r="F5">
+        <v>1792.7</v>
+      </c>
+      <c r="G5">
+        <v>116.49229969458703</v>
+      </c>
+      <c r="H5">
+        <v>112.73718783295546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6">
+        <v>2000</v>
+      </c>
+      <c r="B6">
+        <v>2048.2309409790801</v>
+      </c>
+      <c r="C6">
+        <v>0.32177297173491998</v>
+      </c>
+      <c r="D6">
+        <v>2337717</v>
+      </c>
+      <c r="E6">
+        <v>1242695</v>
+      </c>
+      <c r="F6">
+        <v>1850.2</v>
+      </c>
+      <c r="G6">
+        <v>120.22873481057898</v>
+      </c>
+      <c r="H6">
+        <v>105.60479970839857</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7">
+        <v>2001</v>
+      </c>
+      <c r="B7">
+        <v>2094.0262880208202</v>
+      </c>
+      <c r="C7">
+        <v>0.32600000000000001</v>
+      </c>
+      <c r="D7">
+        <v>2376421</v>
+      </c>
+      <c r="E7">
+        <v>1268943</v>
+      </c>
+      <c r="F7">
+        <v>1917.2</v>
+      </c>
+      <c r="G7">
+        <v>124.58249398921306</v>
+      </c>
+      <c r="H7">
+        <v>107.96596336195017</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8">
+        <v>2002</v>
+      </c>
+      <c r="B8">
+        <v>2242.8949786917201</v>
+      </c>
+      <c r="C8">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="D8">
+        <v>2433822</v>
+      </c>
+      <c r="E8">
+        <v>1289405</v>
+      </c>
+      <c r="F8">
+        <v>2090.6999999999998</v>
+      </c>
+      <c r="G8">
+        <v>135.85678081746698</v>
+      </c>
+      <c r="H8">
+        <v>115.64148859038801</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9">
+        <v>2003</v>
+      </c>
+      <c r="B9">
+        <v>2381.2204626807302</v>
+      </c>
+      <c r="C9">
+        <v>0.32926640809331398</v>
+      </c>
+      <c r="D9">
+        <v>2427518.2400000002</v>
+      </c>
+      <c r="E9">
+        <v>1287365.05</v>
+      </c>
+      <c r="F9">
+        <v>2281.5</v>
+      </c>
+      <c r="G9">
+        <v>148.25524725453246</v>
+      </c>
+      <c r="H9">
+        <v>122.77341631346204</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10">
+        <v>2004</v>
+      </c>
+      <c r="B10">
+        <v>2544.2359787298101</v>
+      </c>
+      <c r="C10">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="D10">
+        <v>2361377</v>
+      </c>
+      <c r="E10">
+        <v>1245875</v>
+      </c>
+      <c r="F10">
+        <v>2441.9</v>
+      </c>
+      <c r="G10">
+        <v>158.67827669114303</v>
+      </c>
+      <c r="H10">
+        <v>131.17833813028375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11">
+        <v>2005</v>
+      </c>
+      <c r="B11">
+        <v>2633.0518524427398</v>
+      </c>
+      <c r="C11">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="D11">
+        <v>2262160</v>
+      </c>
+      <c r="E11">
+        <v>1215989</v>
+      </c>
+      <c r="F11">
+        <v>2487.5</v>
+      </c>
+      <c r="G11">
+        <v>161.64143219182532</v>
+      </c>
+      <c r="H11">
+        <v>135.75759839177402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <v>2006</v>
+      </c>
+      <c r="B12">
+        <v>2797.67399496903</v>
+      </c>
+      <c r="C12">
+        <v>0.29129080881841002</v>
+      </c>
+      <c r="D12">
+        <v>2178397</v>
+      </c>
+      <c r="E12">
+        <v>1182675</v>
+      </c>
+      <c r="F12">
+        <v>2582.6999999999998</v>
+      </c>
+      <c r="G12">
+        <v>167.82766911430241</v>
+      </c>
+      <c r="H12">
+        <v>144.2453563106863</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <v>2007</v>
+      </c>
+      <c r="B13">
+        <v>2791.2678099876298</v>
+      </c>
+      <c r="C13">
+        <v>0.30161607339582402</v>
+      </c>
+      <c r="D13">
+        <v>2271950</v>
+      </c>
+      <c r="E13">
+        <v>1225436</v>
+      </c>
+      <c r="F13">
+        <v>2612.1</v>
+      </c>
+      <c r="G13">
+        <v>169.73812463447914</v>
+      </c>
+      <c r="H13">
+        <v>143.91505962962341</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14">
+        <v>2008</v>
+      </c>
+      <c r="B14">
+        <v>2804.6035641015301</v>
+      </c>
+      <c r="C14">
+        <v>0.29579460935900997</v>
+      </c>
+      <c r="D14">
+        <v>2249481</v>
+      </c>
+      <c r="E14">
+        <v>1211669.9745008899</v>
+      </c>
+      <c r="F14">
+        <v>2585.8000000000002</v>
+      </c>
+      <c r="G14">
+        <v>168.0291117031646</v>
+      </c>
+      <c r="H14">
+        <v>144.60263817068662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15">
+        <v>2009</v>
+      </c>
+      <c r="B15">
+        <v>2881.37483489749</v>
+      </c>
+      <c r="C15">
+        <v>0.29250672209346601</v>
+      </c>
+      <c r="D15">
+        <v>2254890</v>
+      </c>
+      <c r="E15">
+        <v>1229418</v>
+      </c>
+      <c r="F15">
+        <v>2610.6</v>
+      </c>
+      <c r="G15">
+        <v>169.64065241406198</v>
+      </c>
+      <c r="H15">
+        <v>148.56089039389107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16">
+        <v>2010</v>
+      </c>
+      <c r="B16">
+        <v>3132.27450749729</v>
+      </c>
+      <c r="C16">
+        <v>0.29760312239746101</v>
+      </c>
+      <c r="D16">
+        <v>2315252</v>
+      </c>
+      <c r="E16">
+        <v>1270592</v>
+      </c>
+      <c r="F16">
+        <v>2834.5</v>
+      </c>
+      <c r="G16">
+        <v>184.19000584833321</v>
+      </c>
+      <c r="H16">
+        <v>161.4970340394602</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A17">
+        <v>2011</v>
+      </c>
+      <c r="B17">
+        <v>3193.95764656032</v>
+      </c>
+      <c r="C17">
+        <v>0.289171993173439</v>
+      </c>
+      <c r="D17">
+        <v>2273693</v>
+      </c>
+      <c r="E17">
+        <v>1274390</v>
+      </c>
+      <c r="F17">
+        <v>3005.4</v>
+      </c>
+      <c r="G17">
+        <v>195.29534082786407</v>
+      </c>
+      <c r="H17">
+        <v>164.67735683207596</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A18">
+        <v>2012</v>
+      </c>
+      <c r="B18">
+        <v>3165.8711063220499</v>
+      </c>
+      <c r="C18">
+        <v>0.290193541595889</v>
+      </c>
+      <c r="D18">
+        <v>2308013.1255999999</v>
+      </c>
+      <c r="E18">
+        <v>1317820.2429706501</v>
+      </c>
+      <c r="F18">
+        <v>3075.2</v>
+      </c>
+      <c r="G18">
+        <v>199.83104815127686</v>
+      </c>
+      <c r="H18">
+        <v>163.2292420726404</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A19">
+        <v>2013</v>
+      </c>
+      <c r="B19">
+        <v>3187.5194430697302</v>
+      </c>
+      <c r="C19">
+        <v>0.28005209174053602</v>
+      </c>
+      <c r="D19">
+        <v>2253279</v>
+      </c>
+      <c r="E19">
+        <v>1307345</v>
+      </c>
+      <c r="F19">
+        <v>3105.2131200339913</v>
+      </c>
+      <c r="G19">
+        <v>201.78134511885054</v>
+      </c>
+      <c r="H19">
+        <v>164.34540930775009</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A20">
+        <v>2014</v>
+      </c>
+      <c r="B20">
+        <v>3253.7042597637401</v>
+      </c>
+      <c r="C20">
+        <v>0.26864722758837101</v>
+      </c>
+      <c r="D20">
+        <v>2191164</v>
+      </c>
+      <c r="E20">
+        <v>1285045.09537876</v>
+      </c>
+      <c r="F20">
+        <v>3172.4254496079743</v>
+      </c>
+      <c r="G20">
+        <v>206.14890178750889</v>
+      </c>
+      <c r="H20">
+        <v>167.75783423057982</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A21">
+        <v>2015</v>
+      </c>
+      <c r="B21">
+        <v>3214.3807593094598</v>
+      </c>
+      <c r="C21">
+        <v>0.26948753288994298</v>
+      </c>
+      <c r="D21">
+        <v>2222034.23149388</v>
+      </c>
+      <c r="E21">
+        <v>1341923.3549569</v>
+      </c>
+      <c r="F21">
+        <v>3288.9239176799479</v>
+      </c>
+      <c r="G21">
+        <v>213.71914469295911</v>
+      </c>
+      <c r="H21">
+        <v>165.73035270678139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <v>2016</v>
+      </c>
+      <c r="B22">
+        <v>3275.6984648533198</v>
+      </c>
+      <c r="C22">
+        <v>0.27341481536246298</v>
+      </c>
+      <c r="D22">
+        <v>2278684</v>
+      </c>
+      <c r="E22">
+        <v>1376090</v>
+      </c>
+      <c r="F22">
+        <v>3441.9519080398636</v>
+      </c>
+      <c r="G22">
+        <v>223.66313003053241</v>
+      </c>
+      <c r="H22">
+        <v>168.89183410176634</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <v>2017</v>
+      </c>
+      <c r="B23">
+        <v>3471.8424655563199</v>
+      </c>
+      <c r="C23">
+        <v>0.26400000000000001</v>
+      </c>
+      <c r="D23">
+        <v>2217239</v>
+      </c>
+      <c r="E23">
+        <v>1350642.8119999999</v>
+      </c>
+      <c r="F23">
+        <v>3604.655778256471</v>
+      </c>
+      <c r="G23">
+        <v>234.23586836418679</v>
+      </c>
+      <c r="H23">
+        <v>179.00482843937891</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <v>2018</v>
+      </c>
+      <c r="B24">
+        <v>3666.95876719238</v>
+      </c>
+      <c r="C24">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="D24">
+        <v>2219531.23</v>
+      </c>
+      <c r="E24">
+        <v>1346881.36</v>
+      </c>
+      <c r="F24">
+        <v>3735.3978353999969</v>
+      </c>
+      <c r="G24">
+        <v>242.73168077197974</v>
+      </c>
+      <c r="H24">
+        <v>189.06483561038183</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <v>2019</v>
+      </c>
+      <c r="B25">
+        <v>3773.3038481726599</v>
+      </c>
+      <c r="C25">
+        <v>0.27200000000000002</v>
+      </c>
+      <c r="D25">
+        <v>2317981</v>
+      </c>
+      <c r="E25">
+        <v>1376650.912</v>
+      </c>
+      <c r="F25">
+        <v>3772.0445418656195</v>
+      </c>
+      <c r="G25">
+        <v>245.11303800543368</v>
+      </c>
+      <c r="H25">
+        <v>194.54788478818966</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <v>2020</v>
+      </c>
+      <c r="B26">
+        <v>3803.2729826528098</v>
+      </c>
+      <c r="C26">
+        <v>0.27605180460135997</v>
+      </c>
+      <c r="D26">
+        <v>2371506.6604194902</v>
+      </c>
+      <c r="E26">
+        <v>1436808.6801511699</v>
+      </c>
+      <c r="F26">
+        <v>3777.0080979641098</v>
+      </c>
+      <c r="G26">
+        <v>245.43557722815709</v>
+      </c>
+      <c r="H26">
+        <v>196.09306427986232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <v>2021</v>
+      </c>
+      <c r="B27">
+        <v>3911.9067117239902</v>
+      </c>
+      <c r="C27">
+        <v>0.27098766033190402</v>
+      </c>
+      <c r="D27">
+        <v>2345339.9541282798</v>
+      </c>
+      <c r="E27">
+        <v>1378238.5077107099</v>
+      </c>
+      <c r="F27">
+        <v>3787.7759467155543</v>
+      </c>
+      <c r="G27">
+        <v>246.13528797943687</v>
+      </c>
+      <c r="H27">
+        <v>201.69411393232707</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <v>2022</v>
+      </c>
+      <c r="B28">
+        <v>3961.8086656966698</v>
+      </c>
+      <c r="C28">
+        <v>0.25731537527015802</v>
+      </c>
+      <c r="D28">
+        <v>2260584.4909363398</v>
+      </c>
+      <c r="E28">
+        <v>1351312.7577170799</v>
+      </c>
+      <c r="F28">
+        <v>3766.2140632537175</v>
+      </c>
+      <c r="G28">
+        <v>244.73416487450243</v>
+      </c>
+      <c r="H28">
+        <v>204.26701025417614</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <v>2023</v>
+      </c>
+      <c r="B29">
+        <v>4125.7598031592597</v>
+      </c>
+      <c r="C29">
+        <v>0.27530839632178999</v>
+      </c>
+      <c r="D29">
+        <v>2452735.5703328401</v>
+      </c>
+      <c r="E29">
+        <v>1439228.27368988</v>
+      </c>
+      <c r="F29">
+        <v>3963.104277768432</v>
+      </c>
+      <c r="G29">
+        <v>257.52838246594524</v>
+      </c>
+      <c r="H29">
+        <v>212.72017180314907</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>